--- a/web/files/九龙-何文田-誉林.xlsx
+++ b/web/files/九龙-何文田-誉林.xlsx
@@ -4171,38 +4171,30 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>17118000</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>24008</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K57" s="5" t="n">
+        <v>17118000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>24008</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4211,7 +4203,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4344,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4362,7 +4354,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4985,12 +4977,12 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 713呎 (3房)
-招标单位
--
-(在售)</t>
+$1712万
+$24,008/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">

--- a/web/files/九龙-何文田-誉林.xlsx
+++ b/web/files/九龙-何文田-誉林.xlsx
@@ -1419,38 +1419,30 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>18655000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>26726</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K13" s="5" t="n">
+        <v>18655000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>26726</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1459,7 +1451,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4336,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4354,7 +4346,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4500,12 +4492,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 698呎 (3房)
-招标单位
--
-(在售)</t>
+$1866万
+$26,726/呎
+(26年-10月-01日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">

--- a/web/files/九龙-何文田-誉林.xlsx
+++ b/web/files/九龙-何文田-誉林.xlsx
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>17118000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>24008</v>
+        <v>23975</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>17118000</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>24008</v>
+        <v>23975</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4971,9 +4971,9 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>B | 713呎 (3房)
+          <t>B | 714呎 (3房)
 $1712万
-$24,008/呎
+$23,975/呎
 (26年-09月-22日)</t>
         </is>
       </c>

--- a/web/files/九龙-何文田-誉林.xlsx
+++ b/web/files/九龙-何文田-誉林.xlsx
@@ -4168,7 +4168,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4974,7 +4974,7 @@
           <t>B | 714呎 (3房)
 $1712万
 $23,975/呎
-(26年-09月-22日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">

--- a/web/files/九龙-何文田-誉林.xlsx
+++ b/web/files/九龙-何文田-誉林.xlsx
@@ -1101,38 +1101,30 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>47124000</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>34000</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K8" s="5" t="n">
+        <v>47124000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>34000</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1141,7 +1133,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1407,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1424,14 +1416,14 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
         <v>18655000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>26726</v>
+        <v>26688</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1434,7 @@
         <v>18655000</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>26726</v>
+        <v>26688</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -4336,7 +4328,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4346,7 +4338,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4464,12 +4456,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1386呎 (3房)
-招标单位
--
-(在售)</t>
+$4712万
+$34,000/呎
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4494,10 +4486,10 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 698呎 (3房)
+          <t>A | 699呎 (3房)
 $1866万
-$26,726/呎
-(26年-10月-01日)</t>
+$26,688/呎
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">

--- a/web/files/九龙-何文田-誉林.xlsx
+++ b/web/files/九龙-何文田-誉林.xlsx
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1296</v>
+        <v>1336</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>38744000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>29895</v>
+        <v>29000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>38744000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>29895</v>
+        <v>29000</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>15500000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>24219</v>
+        <v>24181</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>15500000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>24219</v>
+        <v>24181</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>20295000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>26881</v>
+        <v>26916</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>20295000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>26881</v>
+        <v>26916</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>18655000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>26688</v>
+        <v>26726</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>18655000</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>26688</v>
+        <v>26726</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>14833000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>23177</v>
+        <v>23140</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>14833000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>23177</v>
+        <v>23140</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>17650000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>25250</v>
+        <v>25287</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>17650000</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>25250</v>
+        <v>25287</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>13051000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>20392</v>
+        <v>20360</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>13051000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>20392</v>
+        <v>20360</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>17959000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>23787</v>
+        <v>23818</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>17959000</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>23787</v>
+        <v>23818</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>16674000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>23854</v>
+        <v>23888</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>16674000</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>23854</v>
+        <v>23888</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>12924000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>20194</v>
+        <v>20162</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>12924000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>20194</v>
+        <v>20162</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>17659000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>23389</v>
+        <v>23420</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>17659000</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>23389</v>
+        <v>23420</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>16337000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>23372</v>
+        <v>23405</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>16337000</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>23372</v>
+        <v>23405</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>13876000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>21681</v>
+        <v>21647</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>13876000</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>21681</v>
+        <v>21647</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>16688000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>22103</v>
+        <v>22133</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>16688000</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>22103</v>
+        <v>22133</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>15783000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>22579</v>
+        <v>22612</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>15783000</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>22579</v>
+        <v>22612</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>12770000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>20465</v>
+        <v>20432</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>12770000</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>20465</v>
+        <v>20432</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>18183000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>24083</v>
+        <v>24115</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>18183000</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>24083</v>
+        <v>24115</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>15620000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>22346</v>
+        <v>22378</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>15620000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>22346</v>
+        <v>22378</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>13574000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>20199</v>
+        <v>20230</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>13574000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>20199</v>
+        <v>20230</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>16344000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>21648</v>
+        <v>21676</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>16344000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>21648</v>
+        <v>21676</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>14881000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>21289</v>
+        <v>21319</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>14881000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>21289</v>
+        <v>21319</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>15871000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>21021</v>
+        <v>21049</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>15871000</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>21021</v>
+        <v>21049</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>14721000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>21060</v>
+        <v>21090</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>14721000</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>21060</v>
+        <v>21090</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>17293000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>22905</v>
+        <v>22935</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>17293000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>22905</v>
+        <v>22935</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>14848000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>21242</v>
+        <v>21272</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>14848000</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>21242</v>
+        <v>21272</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>15540000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>20583</v>
+        <v>20610</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>15540000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>20583</v>
+        <v>20610</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>14699000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>21029</v>
+        <v>21059</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>14699000</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>21029</v>
+        <v>21059</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>17118000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>23975</v>
+        <v>24008</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>17118000</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>23975</v>
+        <v>24008</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>15500000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>23592</v>
+        <v>23628</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>15500000</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>23592</v>
+        <v>23628</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -4466,9 +4466,9 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>B | 1296呎 (3房)
+          <t>B | 1336呎 (3房)
 $3874万
-$29,895/呎
+$29,000/呎
 (25年-11月-19日)</t>
         </is>
       </c>
@@ -4486,17 +4486,17 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 699呎 (3房)
+          <t>A | 698呎 (3房)
 $1866万
-$26,688/呎
+$26,726/呎
 (26年-10月-16日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>B | 755呎 (3房)
+          <t>B | 754呎 (3房)
 $2030万
-$26,881/呎
+$26,916/呎
 (26年-08月-17日)</t>
         </is>
       </c>
@@ -4518,9 +4518,9 @@
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>E | 640呎 (3房)
+          <t>E | 641呎 (3房)
 $1550万
-$24,219/呎
+$24,181/呎
 (26年-06月-24日)</t>
         </is>
       </c>
@@ -4535,9 +4535,9 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 699呎 (3房)
+          <t>A | 698呎 (3房)
 $1765万
-$25,250/呎
+$25,287/呎
 (26年-04月-27日)</t>
         </is>
       </c>
@@ -4567,9 +4567,9 @@
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>E | 640呎 (3房)
+          <t>E | 641呎 (3房)
 $1483万
-$23,177/呎
+$23,140/呎
 (24年-03月-28日)</t>
         </is>
       </c>
@@ -4584,17 +4584,17 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 699呎 (3房)
+          <t>A | 698呎 (3房)
 $1667万
-$23,854/呎
+$23,888/呎
 (24年-05月-03日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>B | 755呎 (3房)
+          <t>B | 754呎 (3房)
 $1796万
-$23,787/呎
+$23,818/呎
 (26年-06月-08日)</t>
         </is>
       </c>
@@ -4616,9 +4616,9 @@
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>E | 640呎 (3房)
+          <t>E | 641呎 (3房)
 $1305万
-$20,392/呎
+$20,360/呎
 (25年-10月-02日)</t>
         </is>
       </c>
@@ -4633,17 +4633,17 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 699呎 (3房)
+          <t>A | 698呎 (3房)
 $1634万
-$23,372/呎
+$23,405/呎
 (26年-01月-27日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>B | 755呎 (3房)
+          <t>B | 754呎 (3房)
 $1766万
-$23,389/呎
+$23,420/呎
 (26年-06月-15日)</t>
         </is>
       </c>
@@ -4665,9 +4665,9 @@
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>E | 640呎 (3房)
+          <t>E | 641呎 (3房)
 $1292万
-$20,194/呎
+$20,162/呎
 (25年-10月-02日)</t>
         </is>
       </c>
@@ -4682,17 +4682,17 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 699呎 (3房)
+          <t>A | 698呎 (3房)
 $1578万
-$22,579/呎
+$22,612/呎
 (24年-03月-21日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>B | 755呎 (3房)
+          <t>B | 754呎 (3房)
 $1669万
-$22,103/呎
+$22,133/呎
 (26年-04月-30日)</t>
         </is>
       </c>
@@ -4714,9 +4714,9 @@
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t>E | 640呎 (3房)
+          <t>E | 641呎 (3房)
 $1388万
-$21,681/呎
+$21,647/呎
 (23年-12月-13日)</t>
         </is>
       </c>
@@ -4731,17 +4731,17 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>A | 699呎 (3房)
+          <t>A | 698呎 (3房)
 $1562万
-$22,346/呎
+$22,378/呎
 (24年-03月-27日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 755呎 (3房)
+          <t>B | 754呎 (3房)
 $1818万
-$24,083/呎
+$24,115/呎
 (24年-04月-22日)</t>
         </is>
       </c>
@@ -4763,9 +4763,9 @@
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>E | 624呎 (3房)
+          <t>E | 625呎 (3房)
 $1277万
-$20,465/呎
+$20,432/呎
 (23年-12月-13日)</t>
         </is>
       </c>
@@ -4780,17 +4780,17 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 699呎 (3房)
+          <t>A | 698呎 (3房)
 $1488万
-$21,289/呎
+$21,319/呎
 (25年-12月-05日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>B | 755呎 (3房)
+          <t>B | 754呎 (3房)
 $1634万
-$21,648/呎
+$21,676/呎
 (23年-12月-11日)</t>
         </is>
       </c>
@@ -4812,9 +4812,9 @@
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>E | 672呎 (3房)
+          <t>E | 671呎 (3房)
 $1357万
-$20,199/呎
+$20,230/呎
 (25年-06月-25日)</t>
         </is>
       </c>
@@ -4829,17 +4829,17 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 699呎 (3房)
+          <t>A | 698呎 (3房)
 $1472万
-$21,060/呎
+$21,090/呎
 (25年-12月-01日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>B | 755呎 (3房)
+          <t>B | 754呎 (3房)
 $1587万
-$21,021/呎
+$21,049/呎
 (26年-02月-13日)</t>
         </is>
       </c>
@@ -4871,17 +4871,17 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>A | 699呎 (3房)
+          <t>A | 698呎 (3房)
 $1485万
-$21,242/呎
+$21,272/呎
 (25年-05月-30日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>B | 755呎 (3房)
+          <t>B | 754呎 (3房)
 $1729万
-$22,905/呎
+$22,935/呎
 (24年-01月-26日)</t>
         </is>
       </c>
@@ -4913,17 +4913,17 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>A | 699呎 (3房)
+          <t>A | 698呎 (3房)
 $1470万
-$21,029/呎
+$21,059/呎
 (24年-04月-09日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>B | 755呎 (3房)
+          <t>B | 754呎 (3房)
 $1554万
-$20,583/呎
+$20,610/呎
 (26年-04月-01日)</t>
         </is>
       </c>
@@ -4955,17 +4955,17 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>A | 657呎 (3房)
+          <t>A | 656呎 (3房)
 $1550万
-$23,592/呎
+$23,628/呎
 (26年-07月-07日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>B | 714呎 (3房)
+          <t>B | 713呎 (3房)
 $1712万
-$23,975/呎
+$24,008/呎
 (26年-10月-16日)</t>
         </is>
       </c>
